--- a/docs/all-profiles.xlsx
+++ b/docs/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-02T16:31:57+01:00</t>
+    <t>2025-11-02T18:22:16+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="F52" s="2"/>
       <c r="G52" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -13135,7 +13135,7 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>86</v>
